--- a/outputs/monitor_xlsx/20260317.xlsx
+++ b/outputs/monitor_xlsx/20260317.xlsx
@@ -544,10 +544,6 @@
           <t>-0.47%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.36%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>-0.69%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.52%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-4.85%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>+0.63%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,7 +671,6 @@
           <t>4.72億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-233.16億</t>
@@ -733,7 +708,6 @@
           <t>2.06億</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>33.05億</t>
@@ -744,8 +718,6 @@
           <t>165.23億</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,15 +735,11 @@
           <t>148.39%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>151.04%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -789,11 +757,6 @@
           <t>97.73億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,15 +774,11 @@
           <t>10697口</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>12700口</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,7 +796,6 @@
           <t>-15.19億</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>-34.93億</t>
@@ -942,10 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1067,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1102,6 +1056,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2341,6 +2296,112 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="E23" t="n">
+        <v>522</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H23" t="n">
+        <v>64</v>
+      </c>
+      <c r="I23" t="n">
+        <v>106</v>
+      </c>
+      <c r="J23" t="n">
+        <v>21</v>
+      </c>
+      <c r="K23" t="n">
+        <v>245</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1260</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-8982</v>
+      </c>
+      <c r="N23" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1470</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5888</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-518</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-801</v>
+      </c>
+      <c r="H24" t="n">
+        <v>516</v>
+      </c>
+      <c r="I24" t="n">
+        <v>281</v>
+      </c>
+      <c r="J24" t="n">
+        <v>146</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3272</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15820</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-106286</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260317.xlsx
+++ b/outputs/monitor_xlsx/20260317.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>33836.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
+          <t>+1.48%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5011.9$</t>
+          <t>321.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+0.36%</t>
-        </is>
-      </c>
+          <t>+1.21%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>33795.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.69%</t>
-        </is>
-      </c>
+          <t>+1.60%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7836.83</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.52%</t>
-        </is>
-      </c>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>5001.0$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-4.85%</t>
-        </is>
-      </c>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>94.09$</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
+          <t>-0.69%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.72億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-233.16億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-1165.78億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-199.89億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3997.76億</t>
-        </is>
-      </c>
+          <t>7836.83</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+0.52%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.06億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>33.05億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>165.23億</t>
-        </is>
-      </c>
+          <t>22.37</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-4.85%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>148.39%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>151.04%</t>
-        </is>
-      </c>
+          <t>96.21$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+2.90%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +765,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>97.73億</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-270.63億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-1353.17億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -766,54 +803,137 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10697口</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12700口</t>
-        </is>
-      </c>
+          <t>7.58億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>37.89億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>151.04%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10697口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>14086口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-15.19億</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-34.93億</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-174.66億</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-7.6億</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-151.91億</t>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-54.24億</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-271.22億</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.56億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-231.27億</t>
         </is>
       </c>
     </row>
@@ -860,7 +980,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-233.16億</t>
+          <t>-270.63億</t>
         </is>
       </c>
     </row>
@@ -872,7 +992,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1165.78億</t>
+          <t>-1353.17億</t>
         </is>
       </c>
     </row>
@@ -884,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-199.89億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -896,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-3997.76億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33.05億</t>
+          <t>7.58億</t>
         </is>
       </c>
     </row>
@@ -920,7 +1044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>165.23億</t>
+          <t>37.89億</t>
         </is>
       </c>
     </row>
@@ -939,7 +1063,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-34.93億</t>
+          <t>-54.24億</t>
         </is>
       </c>
     </row>
@@ -951,7 +1075,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-174.66億</t>
+          <t>-271.22億</t>
         </is>
       </c>
     </row>
@@ -963,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-7.6億</t>
+          <t>-11.56億</t>
         </is>
       </c>
     </row>
@@ -975,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-151.91億</t>
+          <t>-231.27億</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12700口</t>
+          <t>14086口</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1203,13 +1320,13 @@
         <v>-15785</v>
       </c>
       <c r="H4" t="n">
-        <v>-190373</v>
+        <v>-201139</v>
       </c>
       <c r="I4" t="n">
         <v>3850</v>
       </c>
       <c r="J4" t="n">
-        <v>8232</v>
+        <v>7696</v>
       </c>
       <c r="K4" t="n">
         <v>1393</v>
@@ -1218,17 +1335,12 @@
         <v>12753</v>
       </c>
       <c r="M4" t="n">
-        <v>53232</v>
+        <v>54085</v>
       </c>
       <c r="N4" t="n">
         <v>-4477755</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1263,13 +1375,13 @@
         <v>129</v>
       </c>
       <c r="H5" t="n">
-        <v>-726</v>
+        <v>-1114</v>
       </c>
       <c r="I5" t="n">
         <v>-16</v>
       </c>
       <c r="J5" t="n">
-        <v>-292</v>
+        <v>-389</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
@@ -1278,17 +1390,12 @@
         <v>2855</v>
       </c>
       <c r="M5" t="n">
-        <v>11102</v>
+        <v>11195</v>
       </c>
       <c r="N5" t="n">
         <v>-78822</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1323,13 +1430,13 @@
         <v>4060</v>
       </c>
       <c r="H6" t="n">
-        <v>-293</v>
+        <v>-1296</v>
       </c>
       <c r="I6" t="n">
         <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>920</v>
+        <v>-424</v>
       </c>
       <c r="K6" t="n">
         <v>443</v>
@@ -1338,17 +1445,12 @@
         <v>5633</v>
       </c>
       <c r="M6" t="n">
-        <v>23548</v>
+        <v>23620</v>
       </c>
       <c r="N6" t="n">
         <v>-649047</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1383,13 +1485,13 @@
         <v>-230</v>
       </c>
       <c r="H7" t="n">
-        <v>-27731</v>
+        <v>-42936</v>
       </c>
       <c r="I7" t="n">
         <v>-492</v>
       </c>
       <c r="J7" t="n">
-        <v>636</v>
+        <v>-689</v>
       </c>
       <c r="K7" t="n">
         <v>349</v>
@@ -1398,17 +1500,12 @@
         <v>24963</v>
       </c>
       <c r="M7" t="n">
-        <v>99366</v>
+        <v>101045</v>
       </c>
       <c r="N7" t="n">
         <v>-6483125</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1417,12 +1514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1431,44 +1528,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>123.5</v>
+        <v>1455</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5.56</v>
+        <v>4.68</v>
       </c>
       <c r="F8" t="n">
-        <v>236549</v>
+        <v>3563</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>18464</v>
+        <v>1075</v>
       </c>
       <c r="H8" t="n">
-        <v>-41090</v>
+        <v>-2940</v>
       </c>
       <c r="I8" t="n">
-        <v>1425</v>
+        <v>-210</v>
       </c>
       <c r="J8" t="n">
-        <v>-1391</v>
+        <v>-266</v>
       </c>
       <c r="K8" t="n">
-        <v>1395</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>125776</v>
+        <v>2049</v>
       </c>
       <c r="M8" t="n">
-        <v>511809</v>
+        <v>7966</v>
       </c>
       <c r="N8" t="n">
-        <v>-1115462</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140185</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1477,12 +1569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1491,44 +1583,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2700</v>
+        <v>1470</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4.45</v>
+        <v>1.38</v>
       </c>
       <c r="F9" t="n">
-        <v>2921</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>118</v>
+        <v>5888</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-518</v>
       </c>
       <c r="H9" t="n">
-        <v>-1124</v>
+        <v>-283</v>
       </c>
       <c r="I9" t="n">
-        <v>75</v>
+        <v>516</v>
       </c>
       <c r="J9" t="n">
-        <v>828</v>
+        <v>-235</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="L9" t="n">
-        <v>1949</v>
+        <v>3272</v>
       </c>
       <c r="M9" t="n">
-        <v>7554</v>
+        <v>12548</v>
       </c>
       <c r="N9" t="n">
-        <v>-89510</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106286</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1537,12 +1624,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1551,44 +1638,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3190</v>
+        <v>2700</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>2.08</v>
+        <v>4.45</v>
       </c>
       <c r="F10" t="n">
-        <v>1118</v>
+        <v>2921</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>659</v>
+        <v>-2261</v>
       </c>
       <c r="I10" t="n">
-        <v>-58</v>
+        <v>75</v>
       </c>
       <c r="J10" t="n">
-        <v>-147</v>
+        <v>531</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="L10" t="n">
-        <v>5764</v>
+        <v>1949</v>
       </c>
       <c r="M10" t="n">
-        <v>23589</v>
+        <v>7901</v>
       </c>
       <c r="N10" t="n">
-        <v>-19748</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89510</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1623,13 +1705,13 @@
         <v>32</v>
       </c>
       <c r="H11" t="n">
-        <v>-11</v>
+        <v>-96</v>
       </c>
       <c r="I11" t="n">
         <v>-12</v>
       </c>
       <c r="J11" t="n">
-        <v>-279</v>
+        <v>-79</v>
       </c>
       <c r="K11" t="n">
         <v>46</v>
@@ -1638,17 +1720,12 @@
         <v>4209</v>
       </c>
       <c r="M11" t="n">
-        <v>17787</v>
+        <v>17620</v>
       </c>
       <c r="N11" t="n">
         <v>-19410</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1657,58 +1734,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1350</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>-10</v>
+        <v>6620</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>7.47</v>
       </c>
       <c r="F12" t="n">
-        <v>1153</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>-39</v>
+        <v>522</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>-980</v>
+        <v>-131</v>
       </c>
       <c r="I12" t="n">
-        <v>-61</v>
+        <v>64</v>
       </c>
       <c r="J12" t="n">
-        <v>1207</v>
+        <v>42</v>
       </c>
       <c r="K12" t="n">
-        <v>-43</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>-271</v>
+        <v>245</v>
       </c>
       <c r="M12" t="n">
-        <v>-114</v>
+        <v>1015</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8982</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1717,12 +1789,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1731,41 +1803,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>136</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1.12</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>1253</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>85</v>
+        <v>2730</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-39</v>
       </c>
       <c r="H13" t="n">
-        <v>804</v>
+        <v>-255</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-61</v>
       </c>
       <c r="J13" t="n">
-        <v>-501</v>
+        <v>-238</v>
       </c>
       <c r="K13" t="n">
-        <v>46</v>
+        <v>-43</v>
       </c>
       <c r="L13" t="n">
-        <v>-7</v>
+        <v>-271</v>
       </c>
       <c r="M13" t="n">
-        <v>-178</v>
+        <v>-208</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1788,25 +1858,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>395</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-7.49</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>26633</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-3086</v>
       </c>
       <c r="H14" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="I14" t="n">
         <v>-912</v>
       </c>
       <c r="J14" t="n">
-        <v>-1644</v>
+        <v>-2172</v>
       </c>
       <c r="K14" t="n">
         <v>-145</v>
@@ -1815,17 +1885,12 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>-208</v>
+        <v>-117</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1834,12 +1899,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1848,44 +1913,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1445</v>
+        <v>974</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>6.64</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>529</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>48</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-412</v>
       </c>
       <c r="H15" t="n">
-        <v>-175</v>
-      </c>
-      <c r="I15" t="n">
-        <v>29</v>
+        <v>1362</v>
       </c>
       <c r="J15" t="n">
-        <v>-67</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L15" t="n">
-        <v>-57</v>
+        <v>18</v>
       </c>
       <c r="M15" t="n">
-        <v>-98</v>
+        <v>-384</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1894,514 +1951,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>192</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>2.67</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>10084</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>-113</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>44</v>
       </c>
       <c r="H16" t="n">
-        <v>-417</v>
+        <v>-60</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>40</v>
+        <v>-25</v>
       </c>
       <c r="L16" t="n">
-        <v>4808</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>16800</v>
+        <v>257</v>
       </c>
       <c r="N16" t="n">
-        <v>-11876</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1455</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3563</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>1075</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-2478</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-210</v>
-      </c>
-      <c r="J17" t="n">
-        <v>98</v>
-      </c>
-      <c r="K17" t="n">
-        <v>42</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2049</v>
-      </c>
-      <c r="M17" t="n">
-        <v>7606</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-140185</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>881</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>-8.23</v>
-      </c>
-      <c r="F18" t="n">
-        <v>12315</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>-2450</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-322</v>
-      </c>
-      <c r="I18" t="n">
-        <v>334</v>
-      </c>
-      <c r="J18" t="n">
-        <v>90</v>
-      </c>
-      <c r="K18" t="n">
-        <v>23</v>
-      </c>
-      <c r="L18" t="n">
-        <v>303</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-410</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>929</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>-3.63</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6387</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>-2060</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-1979</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-959</v>
-      </c>
-      <c r="J19" t="n">
-        <v>469</v>
-      </c>
-      <c r="K19" t="n">
-        <v>437</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2580</v>
-      </c>
-      <c r="M19" t="n">
-        <v>8064</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-47629</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1572</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="H20" t="n">
-        <v>72</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L20" t="n">
-        <v>10</v>
-      </c>
-      <c r="M20" t="n">
-        <v>71</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>681</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>-6.97</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1910</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>-412</v>
-      </c>
-      <c r="H21" t="n">
-        <v>737</v>
-      </c>
-      <c r="J21" t="n">
-        <v>144</v>
-      </c>
-      <c r="K21" t="n">
-        <v>24</v>
-      </c>
-      <c r="L21" t="n">
-        <v>18</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-284</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>254.5</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F22" t="n">
-        <v>7876</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>-215</v>
-      </c>
-      <c r="H22" t="n">
-        <v>684</v>
-      </c>
-      <c r="J22" t="n">
-        <v>52</v>
-      </c>
-      <c r="K22" t="n">
-        <v>113</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7004</v>
-      </c>
-      <c r="M22" t="n">
-        <v>29941</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-58885</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>6620</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="E23" t="n">
-        <v>522</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H23" t="n">
-        <v>64</v>
-      </c>
-      <c r="I23" t="n">
-        <v>106</v>
-      </c>
-      <c r="J23" t="n">
-        <v>21</v>
-      </c>
-      <c r="K23" t="n">
-        <v>245</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1260</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-8982</v>
-      </c>
-      <c r="N23" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1470</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5888</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>-518</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-801</v>
-      </c>
-      <c r="H24" t="n">
-        <v>516</v>
-      </c>
-      <c r="I24" t="n">
-        <v>281</v>
-      </c>
-      <c r="J24" t="n">
-        <v>146</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3272</v>
-      </c>
-      <c r="L24" t="n">
-        <v>15820</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-106286</v>
-      </c>
-      <c r="N24" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260317.xlsx
+++ b/outputs/monitor_xlsx/20260317.xlsx
@@ -544,10 +544,6 @@
           <t>+1.48%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+1.21%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+1.60%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-0.47%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+0.14%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.69%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+0.52%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-4.85%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+2.90%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-270.63億</t>
@@ -811,7 +774,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>7.58億</t>
@@ -822,8 +784,6 @@
           <t>37.89億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>151.04%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>10697口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>14086口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-54.24億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>331</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-286</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-3268</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1156</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8869</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40265</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21960</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260317.xlsx
+++ b/outputs/monitor_xlsx/20260317.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>76.65000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>1.39</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>63986</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-15785</v>
       </c>
       <c r="H4" t="n">
-        <v>-201139</v>
+        <v>-216925</v>
       </c>
       <c r="I4" t="n">
         <v>3850</v>
       </c>
       <c r="J4" t="n">
-        <v>7696</v>
+        <v>11546</v>
       </c>
       <c r="K4" t="n">
         <v>1393</v>
@@ -1279,11 +1278,14 @@
         <v>12753</v>
       </c>
       <c r="M4" t="n">
-        <v>54085</v>
+        <v>66838</v>
       </c>
       <c r="N4" t="n">
         <v>-4477755</v>
       </c>
+      <c r="O4" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>921</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1.32</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>1931</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>129</v>
       </c>
       <c r="H5" t="n">
-        <v>-1114</v>
+        <v>-984</v>
       </c>
       <c r="I5" t="n">
         <v>-16</v>
       </c>
       <c r="J5" t="n">
-        <v>-389</v>
+        <v>-405</v>
       </c>
       <c r="K5" t="n">
         <v>23</v>
@@ -1334,11 +1336,14 @@
         <v>2855</v>
       </c>
       <c r="M5" t="n">
-        <v>11195</v>
+        <v>14050</v>
       </c>
       <c r="N5" t="n">
         <v>-78822</v>
       </c>
+      <c r="O5" t="n">
+        <v>-3.14</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1440</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>5.88</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>13512</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>4060</v>
       </c>
       <c r="H6" t="n">
-        <v>-1296</v>
+        <v>2763</v>
       </c>
       <c r="I6" t="n">
         <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>-424</v>
+        <v>-410</v>
       </c>
       <c r="K6" t="n">
         <v>443</v>
@@ -1389,11 +1394,14 @@
         <v>5633</v>
       </c>
       <c r="M6" t="n">
-        <v>23620</v>
+        <v>29253</v>
       </c>
       <c r="N6" t="n">
         <v>-649047</v>
       </c>
+      <c r="O6" t="n">
+        <v>8.76</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1422,20 +1430,20 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>26754</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>-230</v>
       </c>
       <c r="H7" t="n">
-        <v>-42936</v>
+        <v>-43167</v>
       </c>
       <c r="I7" t="n">
         <v>-492</v>
       </c>
       <c r="J7" t="n">
-        <v>-689</v>
+        <v>-1181</v>
       </c>
       <c r="K7" t="n">
         <v>349</v>
@@ -1444,11 +1452,14 @@
         <v>24963</v>
       </c>
       <c r="M7" t="n">
-        <v>101045</v>
+        <v>126008</v>
       </c>
       <c r="N7" t="n">
         <v>-6483125</v>
       </c>
+      <c r="O7" t="n">
+        <v>-1.31</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1455</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>4.68</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>3563</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1075</v>
       </c>
       <c r="H8" t="n">
-        <v>-2940</v>
+        <v>-1864</v>
       </c>
       <c r="I8" t="n">
         <v>-210</v>
       </c>
       <c r="J8" t="n">
-        <v>-266</v>
+        <v>-476</v>
       </c>
       <c r="K8" t="n">
         <v>42</v>
@@ -1499,11 +1510,14 @@
         <v>2049</v>
       </c>
       <c r="M8" t="n">
-        <v>7966</v>
+        <v>10015</v>
       </c>
       <c r="N8" t="n">
         <v>-140185</v>
       </c>
+      <c r="O8" t="n">
+        <v>3.61</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1470</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1.38</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>5888</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-518</v>
       </c>
       <c r="H9" t="n">
-        <v>-283</v>
+        <v>-801</v>
       </c>
       <c r="I9" t="n">
         <v>516</v>
       </c>
       <c r="J9" t="n">
-        <v>-235</v>
+        <v>281</v>
       </c>
       <c r="K9" t="n">
         <v>146</v>
@@ -1554,11 +1568,14 @@
         <v>3272</v>
       </c>
       <c r="M9" t="n">
-        <v>12548</v>
+        <v>15820</v>
       </c>
       <c r="N9" t="n">
         <v>-106286</v>
       </c>
+      <c r="O9" t="n">
+        <v>12.33</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2700</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>4.45</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>2921</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>-2261</v>
+        <v>-2143</v>
       </c>
       <c r="I10" t="n">
         <v>75</v>
       </c>
       <c r="J10" t="n">
-        <v>531</v>
+        <v>606</v>
       </c>
       <c r="K10" t="n">
         <v>113</v>
@@ -1609,11 +1626,14 @@
         <v>1949</v>
       </c>
       <c r="M10" t="n">
-        <v>7901</v>
+        <v>9850</v>
       </c>
       <c r="N10" t="n">
         <v>-89510</v>
       </c>
+      <c r="O10" t="n">
+        <v>15.25</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>1685</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>-2.88</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>822</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>32</v>
       </c>
       <c r="H11" t="n">
-        <v>-96</v>
+        <v>-64</v>
       </c>
       <c r="I11" t="n">
         <v>-12</v>
       </c>
       <c r="J11" t="n">
-        <v>-79</v>
+        <v>-91</v>
       </c>
       <c r="K11" t="n">
         <v>46</v>
@@ -1664,11 +1684,14 @@
         <v>4209</v>
       </c>
       <c r="M11" t="n">
-        <v>17620</v>
+        <v>21829</v>
       </c>
       <c r="N11" t="n">
         <v>-19410</v>
       </c>
+      <c r="O11" t="n">
+        <v>-12.38</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>6620</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>7.47</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>522</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>-131</v>
+        <v>-112</v>
       </c>
       <c r="I12" t="n">
         <v>64</v>
       </c>
       <c r="J12" t="n">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="K12" t="n">
         <v>21</v>
@@ -1719,11 +1742,14 @@
         <v>245</v>
       </c>
       <c r="M12" t="n">
-        <v>1015</v>
+        <v>1260</v>
       </c>
       <c r="N12" t="n">
         <v>-8982</v>
       </c>
+      <c r="O12" t="n">
+        <v>26.69</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-39</v>
       </c>
       <c r="H13" t="n">
-        <v>-255</v>
+        <v>-294</v>
       </c>
       <c r="I13" t="n">
         <v>-61</v>
       </c>
       <c r="J13" t="n">
-        <v>-238</v>
+        <v>-299</v>
       </c>
       <c r="K13" t="n">
         <v>-43</v>
@@ -1774,11 +1800,14 @@
         <v>-271</v>
       </c>
       <c r="M13" t="n">
-        <v>-208</v>
+        <v>-479</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-3086</v>
       </c>
       <c r="H14" t="n">
-        <v>-29</v>
+        <v>-3115</v>
       </c>
       <c r="I14" t="n">
         <v>-912</v>
       </c>
       <c r="J14" t="n">
-        <v>-2172</v>
+        <v>-3084</v>
       </c>
       <c r="K14" t="n">
         <v>-145</v>
@@ -1829,11 +1858,14 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>-117</v>
+        <v>-46</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1856,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-412</v>
       </c>
       <c r="H15" t="n">
-        <v>1362</v>
+        <v>950</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1881,11 +1916,14 @@
         <v>18</v>
       </c>
       <c r="M15" t="n">
-        <v>-384</v>
+        <v>-366</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>44</v>
       </c>
       <c r="H16" t="n">
-        <v>-60</v>
+        <v>-16</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1933,11 +1974,14 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>331</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>-9.81</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>1639</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-286</v>
       </c>
-      <c r="G17" t="n">
-        <v>-3268</v>
-      </c>
       <c r="H17" t="n">
+        <v>-2776</v>
+      </c>
+      <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>1156</v>
-      </c>
       <c r="J17" t="n">
+        <v>1243</v>
+      </c>
+      <c r="K17" t="n">
         <v>28</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8869</v>
       </c>
-      <c r="L17" t="n">
-        <v>40265</v>
-      </c>
       <c r="M17" t="n">
+        <v>42358</v>
+      </c>
+      <c r="N17" t="n">
         <v>-21960</v>
       </c>
-      <c r="N17" t="n">
-        <v>9.92</v>
+      <c r="O17" t="n">
+        <v>11.07</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260317.xlsx
+++ b/outputs/monitor_xlsx/20260317.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>11.07</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4685</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-544</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-6386</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-113</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-949</v>
+      </c>
+      <c r="K18" t="n">
+        <v>104</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5983</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29669</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400945</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>543</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="F19" t="n">
+        <v>62525</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-1513</v>
+      </c>
+      <c r="H19" t="n">
+        <v>13075</v>
+      </c>
+      <c r="I19" t="n">
+        <v>285</v>
+      </c>
+      <c r="J19" t="n">
+        <v>457</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2253</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35360</v>
+      </c>
+      <c r="M19" t="n">
+        <v>181069</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392549</v>
+      </c>
+      <c r="O19" t="n">
+        <v>16.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>544</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="F20" t="n">
+        <v>29422</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-4788</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-9760</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1085</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5807</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1174</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10484</v>
+      </c>
+      <c r="M20" t="n">
+        <v>46626</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161304</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11.85</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
